--- a/credit_cards.xlsx
+++ b/credit_cards.xlsx
@@ -1,41 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MINEDUCYT\Downloads\Theproyect\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD25D50-1CE8-4503-80C4-1A44481FBFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Tarjetas" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>Nombre en la Tarjeta</t>
+  </si>
+  <si>
+    <t>Número de Tarjeta</t>
+  </si>
+  <si>
+    <t>Fecha de Expiración</t>
+  </si>
+  <si>
+    <t>CVV</t>
+  </si>
+  <si>
+    <t>Elizabeth Aracely Menjívar Melara</t>
+  </si>
+  <si>
+    <t>4319920001961017</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>621</t>
+  </si>
+  <si>
+    <t>Alberto Rosales Angeles Acosta</t>
+  </si>
+  <si>
+    <t>12312454643</t>
+  </si>
+  <si>
+    <t>11/28</t>
+  </si>
+  <si>
+    <t>792</t>
+  </si>
+  <si>
+    <t>Wilfredo Elias de jesus</t>
+  </si>
+  <si>
+    <t>32145698736</t>
+  </si>
+  <si>
+    <t>12/30</t>
+  </si>
+  <si>
+    <t>987</t>
+  </si>
+  <si>
+    <t>Mateo Antonio Menjívar Melara</t>
+  </si>
+  <si>
+    <t>321765987345</t>
+  </si>
+  <si>
+    <t>12/29</t>
+  </si>
+  <si>
+    <t>984</t>
+  </si>
+  <si>
+    <t>MATEO ANTONIO</t>
+  </si>
+  <si>
+    <t>8293719239712</t>
+  </si>
+  <si>
+    <t>29/29</t>
+  </si>
+  <si>
+    <t>876</t>
+  </si>
+  <si>
+    <t>Elizabeth Aracely Melaza John</t>
+  </si>
+  <si>
+    <t>7896543121243</t>
+  </si>
+  <si>
+    <t>12/28</t>
+  </si>
+  <si>
+    <t>652</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +140,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,55 +479,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nombre en la Tarjeta</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Número de Tarjeta</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Fecha de Expiración</v>
-      </c>
-      <c r="D1" t="str">
-        <v>CVV</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Elizabeth Aracely Menjívar Melara</v>
-      </c>
-      <c r="B2" t="str">
-        <v>4319920001961017</v>
-      </c>
-      <c r="C2" t="str">
-        <v>1124</v>
-      </c>
-      <c r="D2" t="str">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Alberto Rosales Angeles Acosta</v>
-      </c>
-      <c r="B3" t="str">
-        <v>12312454643</v>
-      </c>
-      <c r="C3" t="str">
-        <v>11/28</v>
-      </c>
-      <c r="D3" t="str">
-        <v>792</v>
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError sqref="A1:D8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/credit_cards.xlsx
+++ b/credit_cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MINEDUCYT\Downloads\Theproyect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD25D50-1CE8-4503-80C4-1A44481FBFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBC7375-FC28-4947-8E7F-10B7BB9C2D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Nombre en la Tarjeta</t>
   </si>
@@ -104,6 +104,30 @@
   </si>
   <si>
     <t>652</t>
+  </si>
+  <si>
+    <t>Paula Sanchez Torre Obradora</t>
+  </si>
+  <si>
+    <t>6750981233514</t>
+  </si>
+  <si>
+    <t>40/27</t>
+  </si>
+  <si>
+    <t>654</t>
+  </si>
+  <si>
+    <t>Alberto Rosales Molinas de Barca</t>
+  </si>
+  <si>
+    <t>456764654678</t>
+  </si>
+  <si>
+    <t>10/30</t>
+  </si>
+  <si>
+    <t>765</t>
   </si>
 </sst>
 </file>
@@ -480,10 +504,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.625" customWidth="1"/>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="4" max="4" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -556,38 +583,66 @@
         <v>19</v>
       </c>
     </row>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D8" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>